--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:46</t>
+    <t xml:space="preserve">2026-09-09 23:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:46</t>
+    <t xml:space="preserve">2026-09-18 10:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:35</t>
+    <t xml:space="preserve">2026-09-23 13:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:07</t>
+    <t xml:space="preserve">2026-10-02 15:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_nuble.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Pinto</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">San Nicolás</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:28</t>
+    <t xml:space="preserve">2026-10-04 09:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:54</t>
+    <t xml:space="preserve">2026-10-05 13:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
